--- a/research/traditional_assets/database/data/malaysia/malaysia_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1146</v>
+        <v>-0.0388</v>
       </c>
       <c r="E2">
-        <v>0.1695</v>
+        <v>-0.0545</v>
+      </c>
+      <c r="F2">
+        <v>-0.227</v>
       </c>
       <c r="G2">
-        <v>0.021222810111699</v>
+        <v>0.07834132967786153</v>
       </c>
       <c r="H2">
-        <v>0.021222810111699</v>
+        <v>0.07833153823558209</v>
       </c>
       <c r="I2">
-        <v>-0.00532039976484421</v>
+        <v>0.07549201997454225</v>
       </c>
       <c r="J2">
-        <v>-0.004668205150723567</v>
+        <v>0.06023774181924508</v>
       </c>
       <c r="K2">
-        <v>128.93</v>
+        <v>58.36</v>
       </c>
       <c r="L2">
-        <v>0.3789829512051734</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="M2">
-        <v>40.209</v>
+        <v>21.57</v>
       </c>
       <c r="N2">
-        <v>0.04870866141732284</v>
+        <v>0.04187536400698894</v>
       </c>
       <c r="O2">
-        <v>0.3118669045218336</v>
+        <v>0.3696024674434544</v>
       </c>
       <c r="P2">
-        <v>32.839</v>
+        <v>21.57</v>
       </c>
       <c r="Q2">
-        <v>0.03978073894609328</v>
+        <v>0.04187536400698894</v>
       </c>
       <c r="R2">
-        <v>0.2547041030016288</v>
+        <v>0.3696024674434544</v>
       </c>
       <c r="S2">
-        <v>7.370000000000003</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.1832922977442862</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>691.7</v>
+        <v>128.8</v>
       </c>
       <c r="V2">
-        <v>0.8379164142943671</v>
+        <v>0.2500485342651912</v>
       </c>
       <c r="W2">
-        <v>0.1208093191801315</v>
+        <v>0.05836753305973552</v>
       </c>
       <c r="X2">
-        <v>0.04260149331591458</v>
+        <v>0.0780519651529783</v>
       </c>
       <c r="Y2">
-        <v>0.0782078258642169</v>
+        <v>-0.01968443209324278</v>
       </c>
       <c r="Z2">
-        <v>0.5715053673123121</v>
+        <v>0.1407272677166439</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03970350915742979</v>
+        <v>0.07519320785139325</v>
       </c>
       <c r="AC2">
-        <v>-0.03970350915742979</v>
+        <v>-0.07519320785139325</v>
       </c>
       <c r="AD2">
-        <v>206.35</v>
+        <v>119.123</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>206.35</v>
+        <v>119.123</v>
       </c>
       <c r="AG2">
-        <v>-485.35</v>
+        <v>-9.677000000000021</v>
       </c>
       <c r="AH2">
-        <v>0.1999806173377914</v>
+        <v>0.1878251025270291</v>
       </c>
       <c r="AI2">
-        <v>0.1630387547900289</v>
+        <v>0.1382542016636046</v>
       </c>
       <c r="AJ2">
-        <v>-1.426870498309569</v>
+        <v>-0.01914633880927465</v>
       </c>
       <c r="AK2">
-        <v>-0.84563115253942</v>
+        <v>-0.01320509863909842</v>
       </c>
       <c r="AL2">
-        <v>3.67</v>
+        <v>3.63</v>
       </c>
       <c r="AM2">
-        <v>-0.04000000000000004</v>
+        <v>-1.01</v>
       </c>
       <c r="AN2">
-        <v>-152.8518518518518</v>
+        <v>14.56271393643032</v>
       </c>
       <c r="AO2">
-        <v>-0.4931880108991826</v>
+        <v>2.123966942148761</v>
       </c>
       <c r="AP2">
-        <v>359.5185185185185</v>
+        <v>-1.183007334963328</v>
       </c>
       <c r="AQ2">
-        <v>45.24999999999996</v>
+        <v>-7.633663366336635</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Apex Equity Holdings Berhad (KLSE:APEX)</t>
+          <t>Insas Berhad (KLSE:INSAS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +725,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.186</v>
+        <v>-0.112</v>
       </c>
       <c r="E3">
-        <v>0.11</v>
+        <v>0.0484</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.1731818181818182</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.1731601731601732</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.1668831168831169</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.1573874321008079</v>
       </c>
       <c r="K3">
-        <v>5.63</v>
+        <v>44.1</v>
       </c>
       <c r="L3">
-        <v>0.2491150442477876</v>
+        <v>0.9545454545454545</v>
       </c>
       <c r="M3">
-        <v>0.969</v>
+        <v>3.57</v>
       </c>
       <c r="N3">
-        <v>0.01811214953271028</v>
+        <v>0.02928630024610336</v>
       </c>
       <c r="O3">
-        <v>0.172113676731794</v>
+        <v>0.08095238095238094</v>
       </c>
       <c r="P3">
-        <v>0.969</v>
+        <v>3.57</v>
       </c>
       <c r="Q3">
-        <v>0.01811214953271028</v>
+        <v>0.02928630024610336</v>
       </c>
       <c r="R3">
-        <v>0.172113676731794</v>
+        <v>0.08095238095238094</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,61 +773,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>46.9</v>
+        <v>38.8</v>
       </c>
       <c r="V3">
-        <v>0.8766355140186916</v>
+        <v>0.3182936833470057</v>
       </c>
       <c r="W3">
-        <v>0.07427440633245383</v>
+        <v>0.08641975308641975</v>
       </c>
       <c r="X3">
-        <v>0.03910428143523309</v>
+        <v>0.09427027957390412</v>
       </c>
       <c r="Y3">
-        <v>0.03517012489722074</v>
+        <v>-0.007850526487484369</v>
       </c>
       <c r="Z3">
-        <v>0.5404112864658058</v>
+        <v>0.09148877183254783</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>0.01439918286478143</v>
       </c>
       <c r="AB3">
-        <v>0.03876949626164448</v>
+        <v>0.07505195560143352</v>
       </c>
       <c r="AC3">
-        <v>-0.03876949626164448</v>
+        <v>-0.06065277273665209</v>
       </c>
       <c r="AD3">
-        <v>1.35</v>
+        <v>83.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.35</v>
+        <v>83.8</v>
       </c>
       <c r="AG3">
-        <v>-45.55</v>
+        <v>45</v>
       </c>
       <c r="AH3">
-        <v>0.02461257976298997</v>
+        <v>0.4073894020418085</v>
       </c>
       <c r="AI3">
-        <v>0.01659496004917025</v>
+        <v>0.1494027455874487</v>
       </c>
       <c r="AJ3">
-        <v>-5.72955974842767</v>
+        <v>0.2696225284601558</v>
       </c>
       <c r="AK3">
-        <v>-1.322206095791001</v>
+        <v>0.08619038498371959</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-1.01</v>
+      </c>
+      <c r="AN3">
+        <v>10.24449877750611</v>
+      </c>
+      <c r="AO3">
+        <v>2.123966942148761</v>
+      </c>
+      <c r="AP3">
+        <v>5.501222493887531</v>
+      </c>
+      <c r="AQ3">
+        <v>-7.633663366336635</v>
       </c>
     </row>
     <row r="4">
@@ -844,10 +859,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.09519999999999999</v>
+        <v>0.0028</v>
       </c>
       <c r="E4">
-        <v>0.229</v>
+        <v>-0.0545</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -862,85 +877,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>44.6</v>
+        <v>12.8</v>
       </c>
       <c r="L4">
-        <v>0.6344238975817924</v>
+        <v>0.2661122661122661</v>
       </c>
       <c r="M4">
-        <v>19.31</v>
+        <v>13.2</v>
       </c>
       <c r="N4">
-        <v>0.04686893203883496</v>
+        <v>0.03904170363797693</v>
       </c>
       <c r="O4">
-        <v>0.4329596412556054</v>
+        <v>1.03125</v>
       </c>
       <c r="P4">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="Q4">
-        <v>0.03228155339805826</v>
+        <v>0.03904170363797693</v>
       </c>
       <c r="R4">
-        <v>0.2982062780269059</v>
+        <v>1.03125</v>
       </c>
       <c r="S4">
-        <v>6.010000000000002</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.3112377006732264</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>61.8</v>
+        <v>61.6</v>
       </c>
       <c r="V4">
-        <v>0.15</v>
+        <v>0.1821946169772257</v>
       </c>
       <c r="W4">
-        <v>0.2083138720224194</v>
+        <v>0.05836753305973552</v>
       </c>
       <c r="X4">
-        <v>0.04024708794162392</v>
+        <v>0.0780519651529783</v>
       </c>
       <c r="Y4">
-        <v>0.1680667840807955</v>
+        <v>-0.01968443209324278</v>
       </c>
       <c r="Z4">
-        <v>0.3887199336466685</v>
+        <v>0.2581857219538379</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.03951750881928706</v>
+        <v>0.07519320785139325</v>
       </c>
       <c r="AC4">
-        <v>-0.03951750881928706</v>
+        <v>-0.07519320785139325</v>
       </c>
       <c r="AD4">
-        <v>36.7</v>
+        <v>34.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>36.7</v>
+        <v>34.4</v>
       </c>
       <c r="AG4">
-        <v>-25.09999999999999</v>
+        <v>-27.2</v>
       </c>
       <c r="AH4">
-        <v>0.08179184310229552</v>
+        <v>0.0923489932885906</v>
       </c>
       <c r="AI4">
-        <v>0.143359375</v>
+        <v>0.1487889273356401</v>
       </c>
       <c r="AJ4">
-        <v>-0.06487464461101058</v>
+        <v>-0.08748793824380829</v>
       </c>
       <c r="AK4">
-        <v>-0.1292481977342945</v>
+        <v>-0.160377358490566</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -957,7 +972,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kenanga Investment Bank Berhad (KLSE:KENANGA)</t>
+          <t>Apex Equity Holdings Berhad (KLSE:APEX)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -966,10 +981,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.134</v>
+        <v>-0.0388</v>
       </c>
       <c r="E5">
-        <v>0.283</v>
+        <v>-0.136</v>
+      </c>
+      <c r="F5">
+        <v>-0.227</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -984,225 +1002,91 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>30</v>
+        <v>1.46</v>
       </c>
       <c r="L5">
-        <v>0.1553599171413775</v>
+        <v>0.1864623243933589</v>
       </c>
       <c r="M5">
-        <v>16.76</v>
+        <v>4.8</v>
       </c>
       <c r="N5">
-        <v>0.08151750972762647</v>
+        <v>0.08711433756805807</v>
       </c>
       <c r="O5">
-        <v>0.5586666666666668</v>
+        <v>3.287671232876712</v>
       </c>
       <c r="P5">
-        <v>15.4</v>
+        <v>4.8</v>
       </c>
       <c r="Q5">
-        <v>0.07490272373540856</v>
+        <v>0.08711433756805807</v>
       </c>
       <c r="R5">
-        <v>0.5133333333333333</v>
+        <v>3.287671232876712</v>
       </c>
       <c r="S5">
-        <v>1.360000000000001</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.08114558472553705</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>480.6</v>
+        <v>28.4</v>
       </c>
       <c r="V5">
-        <v>2.337548638132296</v>
+        <v>0.5154264972776769</v>
       </c>
       <c r="W5">
-        <v>0.1298701298701299</v>
+        <v>0.01825</v>
       </c>
       <c r="X5">
-        <v>0.04495589869020524</v>
+        <v>0.07569846398356356</v>
       </c>
       <c r="Y5">
-        <v>0.08491423117992461</v>
+        <v>-0.05744846398356356</v>
       </c>
       <c r="Z5">
-        <v>-2.31812725090036</v>
+        <v>0.2272859216255443</v>
       </c>
       <c r="AA5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.03988950949557252</v>
+        <v>0.07522722672272125</v>
       </c>
       <c r="AC5">
-        <v>-0.03988950949557252</v>
+        <v>-0.07522722672272125</v>
       </c>
       <c r="AD5">
-        <v>72.40000000000001</v>
+        <v>0.923</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>72.40000000000001</v>
+        <v>0.923</v>
       </c>
       <c r="AG5">
-        <v>-408.2</v>
+        <v>-27.477</v>
       </c>
       <c r="AH5">
-        <v>0.260431654676259</v>
+        <v>0.01647537618478125</v>
       </c>
       <c r="AI5">
-        <v>0.2258265751715533</v>
+        <v>0.0132761819829409</v>
       </c>
       <c r="AJ5">
-        <v>2.014807502467917</v>
+        <v>-0.9947145494696445</v>
       </c>
       <c r="AK5">
-        <v>2.55125</v>
+        <v>-0.6681662330082921</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Insas Berhad (KLSE:INSAS)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>-0.0396</v>
-      </c>
-      <c r="E6">
-        <v>0.043</v>
-      </c>
-      <c r="G6">
-        <v>0.133210332103321</v>
-      </c>
-      <c r="H6">
-        <v>0.133210332103321</v>
-      </c>
-      <c r="I6">
-        <v>-0.03339483394833948</v>
-      </c>
-      <c r="J6">
-        <v>-0.03144680196801968</v>
-      </c>
-      <c r="K6">
-        <v>48.7</v>
-      </c>
-      <c r="L6">
-        <v>0.8985239852398524</v>
-      </c>
-      <c r="M6">
-        <v>3.17</v>
-      </c>
-      <c r="N6">
-        <v>0.02053108808290155</v>
-      </c>
-      <c r="O6">
-        <v>0.06509240246406571</v>
-      </c>
-      <c r="P6">
-        <v>3.17</v>
-      </c>
-      <c r="Q6">
-        <v>0.02053108808290155</v>
-      </c>
-      <c r="R6">
-        <v>0.06509240246406571</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>102.4</v>
-      </c>
-      <c r="V6">
-        <v>0.6632124352331606</v>
-      </c>
-      <c r="W6">
-        <v>0.1117485084901331</v>
-      </c>
-      <c r="X6">
-        <v>0.04977052521579704</v>
-      </c>
-      <c r="Y6">
-        <v>0.06197798327433605</v>
-      </c>
-      <c r="Z6">
-        <v>0.1188857205527528</v>
-      </c>
-      <c r="AA6">
-        <v>-0.003738575711047744</v>
-      </c>
-      <c r="AB6">
-        <v>0.04047230895850053</v>
-      </c>
-      <c r="AC6">
-        <v>-0.04421088466954828</v>
-      </c>
-      <c r="AD6">
-        <v>95.90000000000001</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>95.90000000000001</v>
-      </c>
-      <c r="AG6">
-        <v>-6.5</v>
-      </c>
-      <c r="AH6">
-        <v>0.3831402317219337</v>
-      </c>
-      <c r="AI6">
-        <v>0.1578081290110252</v>
-      </c>
-      <c r="AJ6">
-        <v>-0.04394861392832995</v>
-      </c>
-      <c r="AK6">
-        <v>-0.01286364535919256</v>
-      </c>
-      <c r="AL6">
-        <v>3.67</v>
-      </c>
-      <c r="AM6">
-        <v>-0.04000000000000004</v>
-      </c>
-      <c r="AN6">
-        <v>-71.03703703703704</v>
-      </c>
-      <c r="AO6">
-        <v>-0.4931880108991826</v>
-      </c>
-      <c r="AP6">
-        <v>4.814814814814815</v>
-      </c>
-      <c r="AQ6">
-        <v>45.24999999999996</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/malaysia/malaysia_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_brokerage_investment_banking.xlsx
@@ -588,49 +588,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0388</v>
+        <v>0.00657</v>
       </c>
       <c r="E2">
-        <v>-0.0545</v>
+        <v>-0.0144</v>
       </c>
       <c r="F2">
-        <v>-0.227</v>
+        <v>0.134</v>
       </c>
       <c r="G2">
-        <v>0.07834132967786153</v>
+        <v>-0.00148328761556436</v>
       </c>
       <c r="H2">
-        <v>0.07833153823558209</v>
+        <v>-0.001513766128212943</v>
       </c>
       <c r="I2">
-        <v>0.07549201997454225</v>
+        <v>-0.01859189271563548</v>
       </c>
       <c r="J2">
-        <v>0.06023774181924508</v>
+        <v>-0.0160759023228585</v>
       </c>
       <c r="K2">
-        <v>58.36</v>
+        <v>40.56</v>
       </c>
       <c r="L2">
-        <v>0.5714285714285714</v>
+        <v>0.4120694910088388</v>
       </c>
       <c r="M2">
-        <v>21.57</v>
+        <v>13.07</v>
       </c>
       <c r="N2">
-        <v>0.04187536400698894</v>
+        <v>0.03180048661800487</v>
       </c>
       <c r="O2">
-        <v>0.3696024674434544</v>
+        <v>0.3222386587771203</v>
       </c>
       <c r="P2">
-        <v>21.57</v>
+        <v>13.07</v>
       </c>
       <c r="Q2">
-        <v>0.04187536400698894</v>
+        <v>0.03180048661800487</v>
       </c>
       <c r="R2">
-        <v>0.3696024674434544</v>
+        <v>0.3222386587771203</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,73 +639,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>128.8</v>
+        <v>113</v>
       </c>
       <c r="V2">
-        <v>0.2500485342651912</v>
+        <v>0.2749391727493917</v>
       </c>
       <c r="W2">
-        <v>0.05836753305973552</v>
+        <v>0.05627887442251155</v>
       </c>
       <c r="X2">
-        <v>0.0780519651529783</v>
+        <v>0.06613721997328292</v>
       </c>
       <c r="Y2">
-        <v>-0.01968443209324278</v>
+        <v>-0.00985834555077137</v>
       </c>
       <c r="Z2">
-        <v>0.1407272677166439</v>
+        <v>0.1356022334485509</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07519320785139325</v>
+        <v>0.06332639547613923</v>
       </c>
       <c r="AC2">
-        <v>-0.07519320785139325</v>
+        <v>-0.06337759791794992</v>
       </c>
       <c r="AD2">
-        <v>119.123</v>
+        <v>118.27</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>119.123</v>
+        <v>118.27</v>
       </c>
       <c r="AG2">
-        <v>-9.677000000000021</v>
+        <v>5.269999999999996</v>
       </c>
       <c r="AH2">
-        <v>0.1878251025270291</v>
+        <v>0.2234587261700078</v>
       </c>
       <c r="AI2">
-        <v>0.1382542016636046</v>
+        <v>0.1278912594482952</v>
       </c>
       <c r="AJ2">
-        <v>-0.01914633880927465</v>
+        <v>0.01266005236985609</v>
       </c>
       <c r="AK2">
-        <v>-0.01320509863909842</v>
+        <v>0.006491986646463895</v>
       </c>
       <c r="AL2">
-        <v>3.63</v>
+        <v>4.13</v>
       </c>
       <c r="AM2">
-        <v>-1.01</v>
+        <v>-4.100000000000001</v>
       </c>
       <c r="AN2">
-        <v>14.56271393643032</v>
+        <v>-112.6380952380952</v>
       </c>
       <c r="AO2">
-        <v>2.123966942148761</v>
+        <v>-0.4430992736077482</v>
       </c>
       <c r="AP2">
-        <v>-1.183007334963328</v>
+        <v>-5.019047619047615</v>
       </c>
       <c r="AQ2">
-        <v>-7.633663366336635</v>
+        <v>0.4463414634146341</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Insas Berhad (KLSE:INSAS)</t>
+          <t>Hong Leong Capital Berhad (KLSE:HLCAP)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,46 +725,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.112</v>
+        <v>0.0526</v>
       </c>
       <c r="E3">
-        <v>0.0484</v>
+        <v>-0.0556</v>
       </c>
       <c r="G3">
-        <v>0.1731818181818182</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.1731601731601732</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.1668831168831169</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>0.1573874321008079</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>44.1</v>
+        <v>12.1</v>
       </c>
       <c r="L3">
-        <v>0.9545454545454545</v>
+        <v>0.2607758620689655</v>
       </c>
       <c r="M3">
-        <v>3.57</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="N3">
-        <v>0.02928630024610336</v>
+        <v>0.04078666096622488</v>
       </c>
       <c r="O3">
-        <v>0.08095238095238094</v>
+        <v>0.7884297520661157</v>
       </c>
       <c r="P3">
-        <v>3.57</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="Q3">
-        <v>0.02928630024610336</v>
+        <v>0.04078666096622488</v>
       </c>
       <c r="R3">
-        <v>0.08095238095238094</v>
+        <v>0.7884297520661157</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -773,73 +773,61 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>38.8</v>
+        <v>65.7</v>
       </c>
       <c r="V3">
-        <v>0.3182936833470057</v>
+        <v>0.2808892689183412</v>
       </c>
       <c r="W3">
-        <v>0.08641975308641975</v>
+        <v>0.06148373983739837</v>
       </c>
       <c r="X3">
-        <v>0.09427027957390412</v>
+        <v>0.06613721997328292</v>
       </c>
       <c r="Y3">
-        <v>-0.007850526487484369</v>
+        <v>-0.004653480135884555</v>
       </c>
       <c r="Z3">
-        <v>0.09148877183254783</v>
+        <v>0.2855560342174903</v>
       </c>
       <c r="AA3">
-        <v>0.01439918286478143</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07505195560143352</v>
+        <v>0.06332639547613923</v>
       </c>
       <c r="AC3">
-        <v>-0.06065277273665209</v>
+        <v>-0.06332639547613923</v>
       </c>
       <c r="AD3">
-        <v>83.8</v>
+        <v>34.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>83.8</v>
+        <v>34.3</v>
       </c>
       <c r="AG3">
-        <v>45</v>
+        <v>-31.40000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.4073894020418085</v>
+        <v>0.127889634601044</v>
       </c>
       <c r="AI3">
-        <v>0.1494027455874487</v>
+        <v>0.1460817717206133</v>
       </c>
       <c r="AJ3">
-        <v>0.2696225284601558</v>
+        <v>-0.1550617283950617</v>
       </c>
       <c r="AK3">
-        <v>0.08619038498371959</v>
+        <v>-0.1856889414547605</v>
       </c>
       <c r="AL3">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1.01</v>
-      </c>
-      <c r="AN3">
-        <v>10.24449877750611</v>
-      </c>
-      <c r="AO3">
-        <v>2.123966942148761</v>
-      </c>
-      <c r="AP3">
-        <v>5.501222493887531</v>
-      </c>
-      <c r="AQ3">
-        <v>-7.633663366336635</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -850,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hong Leong Capital Berhad (KLSE:HLCAP)</t>
+          <t>Apex Equity Holdings Berhad (KLSE:APEX)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,10 +847,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0028</v>
+        <v>0.00657</v>
       </c>
       <c r="E4">
-        <v>-0.0545</v>
+        <v>-0.0144</v>
+      </c>
+      <c r="F4">
+        <v>0.134</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -877,85 +868,82 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>12.8</v>
+        <v>1.66</v>
       </c>
       <c r="L4">
-        <v>0.2661122661122661</v>
+        <v>0.1858902575587906</v>
       </c>
       <c r="M4">
-        <v>13.2</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.03904170363797693</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>1.03125</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>13.2</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.03904170363797693</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>1.03125</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>61.6</v>
+        <v>14.4</v>
       </c>
       <c r="V4">
-        <v>0.1821946169772257</v>
+        <v>0.3018867924528302</v>
       </c>
       <c r="W4">
-        <v>0.05836753305973552</v>
+        <v>0.02419825072886297</v>
       </c>
       <c r="X4">
-        <v>0.0780519651529783</v>
+        <v>0.06405046069390762</v>
       </c>
       <c r="Y4">
-        <v>-0.01968443209324278</v>
+        <v>-0.03985220996504464</v>
       </c>
       <c r="Z4">
-        <v>0.2581857219538379</v>
+        <v>0.2171534177953943</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07519320785139325</v>
+        <v>0.06337759791794992</v>
       </c>
       <c r="AC4">
-        <v>-0.07519320785139325</v>
+        <v>-0.06337759791794992</v>
       </c>
       <c r="AD4">
-        <v>34.4</v>
+        <v>1.67</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>34.4</v>
+        <v>1.67</v>
       </c>
       <c r="AG4">
-        <v>-27.2</v>
+        <v>-12.73</v>
       </c>
       <c r="AH4">
-        <v>0.0923489932885906</v>
+        <v>0.03382621024913915</v>
       </c>
       <c r="AI4">
-        <v>0.1487889273356401</v>
+        <v>0.02339918733361356</v>
       </c>
       <c r="AJ4">
-        <v>-0.08748793824380829</v>
+        <v>-0.3640263082642265</v>
       </c>
       <c r="AK4">
-        <v>-0.160377358490566</v>
+        <v>-0.2234509390907495</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -972,7 +960,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Apex Equity Holdings Berhad (KLSE:APEX)</t>
+          <t>Insas Berhad (KLSE:INSAS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -981,49 +969,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0388</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="E5">
-        <v>-0.136</v>
-      </c>
-      <c r="F5">
-        <v>-0.227</v>
+        <v>0.101</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>-0.003387470997679814</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>-0.00345707656612529</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>-0.04245939675174014</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>-0.03828445941227138</v>
       </c>
       <c r="K5">
-        <v>1.46</v>
+        <v>26.8</v>
       </c>
       <c r="L5">
-        <v>0.1864623243933589</v>
+        <v>0.6218097447795824</v>
       </c>
       <c r="M5">
-        <v>4.8</v>
+        <v>3.53</v>
       </c>
       <c r="N5">
-        <v>0.08711433756805807</v>
+        <v>0.02727975270479134</v>
       </c>
       <c r="O5">
-        <v>3.287671232876712</v>
+        <v>0.1317164179104477</v>
       </c>
       <c r="P5">
-        <v>4.8</v>
+        <v>3.53</v>
       </c>
       <c r="Q5">
-        <v>0.08711433756805807</v>
+        <v>0.02727975270479134</v>
       </c>
       <c r="R5">
-        <v>3.287671232876712</v>
+        <v>0.1317164179104477</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1032,61 +1017,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>28.4</v>
+        <v>32.9</v>
       </c>
       <c r="V5">
-        <v>0.5154264972776769</v>
+        <v>0.2542503863987635</v>
       </c>
       <c r="W5">
-        <v>0.01825</v>
+        <v>0.05627887442251155</v>
       </c>
       <c r="X5">
-        <v>0.07569846398356356</v>
+        <v>0.07528496980620766</v>
       </c>
       <c r="Y5">
-        <v>-0.05744846398356356</v>
+        <v>-0.01900609538369611</v>
       </c>
       <c r="Z5">
-        <v>0.2272859216255443</v>
+        <v>0.08252594493164325</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>-0.003159461189194839</v>
       </c>
       <c r="AB5">
-        <v>0.07522722672272125</v>
+        <v>0.0631843946846541</v>
       </c>
       <c r="AC5">
-        <v>-0.07522722672272125</v>
+        <v>-0.06634385587384894</v>
       </c>
       <c r="AD5">
-        <v>0.923</v>
+        <v>82.3</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.923</v>
+        <v>82.3</v>
       </c>
       <c r="AG5">
-        <v>-27.477</v>
+        <v>49.4</v>
       </c>
       <c r="AH5">
-        <v>0.01647537618478125</v>
+        <v>0.3887576759565423</v>
       </c>
       <c r="AI5">
-        <v>0.0132761819829409</v>
+        <v>0.1330423537019076</v>
       </c>
       <c r="AJ5">
-        <v>-0.9947145494696445</v>
+        <v>0.2762863534675615</v>
       </c>
       <c r="AK5">
-        <v>-0.6681662330082921</v>
+        <v>0.08434352057367253</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>-4.100000000000001</v>
+      </c>
+      <c r="AN5">
+        <v>-78.38095238095238</v>
+      </c>
+      <c r="AO5">
+        <v>-0.4430992736077482</v>
+      </c>
+      <c r="AP5">
+        <v>-47.04761904761904</v>
+      </c>
+      <c r="AQ5">
+        <v>0.4463414634146341</v>
       </c>
     </row>
   </sheetData>
